--- a/saldo_menor/sinais_saldo_menor_2026-08-07.xlsx
+++ b/saldo_menor/sinais_saldo_menor_2026-08-07.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/saldo_menor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_7D3D394217C86EEE382A12D04B5ED87656CD3AD0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBB4A975-5904-4395-826E-0AC30072429E}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_7D3D394217C86EEE382A12D04B5ED87656CD3AD0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6B2C2CB-C7F0-4EBD-874B-830BBB4C4EFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="105">
   <si>
     <t>Data</t>
   </si>
@@ -117,15 +117,6 @@
   </si>
   <si>
     <t>SOUTH KOREA 2</t>
-  </si>
-  <si>
-    <t>Gimpo FC</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>🟢 Betmines: 1X &amp; UNDER 2.5 (Placar: 1x0 ou 2x0 | Confiança 79.4%)</t>
   </si>
   <si>
     <t>Yongin</t>
@@ -727,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -908,25 +899,25 @@
         <v>29</v>
       </c>
       <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I5">
         <v>1.05</v>
       </c>
       <c r="J5">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -937,37 +928,37 @@
         <v>46241</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I6">
         <v>1.05</v>
       </c>
       <c r="J6">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -978,22 +969,22 @@
         <v>46241</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
       </c>
       <c r="H7">
         <v>2.1</v>
@@ -1002,16 +993,16 @@
         <v>1.05</v>
       </c>
       <c r="J7">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1019,34 +1010,34 @@
         <v>46241</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
         <v>1.05</v>
       </c>
       <c r="J8">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -1060,34 +1051,34 @@
         <v>46241</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9">
-        <v>2.4</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="I9">
         <v>1.05</v>
       </c>
       <c r="J9">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1101,34 +1092,34 @@
         <v>46241</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H10">
-        <v>2.1800000000000002</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I10">
         <v>1.05</v>
       </c>
       <c r="J10">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -1142,25 +1133,25 @@
         <v>46241</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11">
-        <v>2.4500000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="I11">
         <v>1.05</v>
@@ -1169,7 +1160,7 @@
         <v>1.7</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -1183,40 +1174,40 @@
         <v>46241</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
         <v>60</v>
       </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" t="s">
-        <v>59</v>
-      </c>
       <c r="H12">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="I12">
         <v>1.05</v>
       </c>
       <c r="J12">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1224,34 +1215,34 @@
         <v>46241</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H13">
-        <v>1.83</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="J13">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1265,40 +1256,40 @@
         <v>46241</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14">
-        <v>2.5499999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="J14">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="K14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1306,34 +1297,34 @@
         <v>46241</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H15">
-        <v>2.2000000000000002</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="J15">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="K15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1347,34 +1338,34 @@
         <v>46241</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16">
-        <v>2.5499999999999998</v>
+        <v>1.91</v>
       </c>
       <c r="I16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="J16">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="K16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L16">
         <v>1</v>
@@ -1388,40 +1379,40 @@
         <v>46241</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H17">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="I17">
         <v>1.05</v>
       </c>
       <c r="J17">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="K17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1429,40 +1420,40 @@
         <v>46241</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H18">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="I18">
         <v>1.05</v>
       </c>
       <c r="J18">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
       <c r="K18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1470,34 +1461,34 @@
         <v>46241</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
         <v>94</v>
       </c>
       <c r="H19">
-        <v>2.4</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="I19">
         <v>1.05</v>
       </c>
       <c r="J19">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="K19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L19">
         <v>1</v>
@@ -1511,34 +1502,34 @@
         <v>46241</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H20">
-        <v>2.1800000000000002</v>
+        <v>1.98</v>
       </c>
       <c r="I20">
         <v>1.05</v>
       </c>
       <c r="J20">
-        <v>1.65</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="K20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -1552,80 +1543,39 @@
         <v>46241</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" t="s">
         <v>103</v>
       </c>
-      <c r="F21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s">
-        <v>102</v>
-      </c>
       <c r="H21">
-        <v>1.98</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="I21">
         <v>1.05</v>
       </c>
       <c r="J21">
-        <v>1.1100000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="K21" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="L21">
         <v>1</v>
       </c>
       <c r="M21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>46241</v>
-      </c>
-      <c r="B22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" t="s">
-        <v>106</v>
-      </c>
-      <c r="H22">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="I22">
-        <v>1.05</v>
-      </c>
-      <c r="J22">
-        <v>1.61</v>
-      </c>
-      <c r="K22" t="s">
-        <v>52</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
         <v>1</v>
       </c>
     </row>
